--- a/output/roomself_excel/13145.xlsx
+++ b/output/roomself_excel/13145.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>90423</v>
+        <v>178618</v>
       </c>
       <c r="D2" t="n">
-        <v>2624</v>
+        <v>3748</v>
       </c>
       <c r="E2" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F2" t="n">
-        <v>208</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>132312</v>
+        <v>219571</v>
       </c>
       <c r="D3" t="n">
-        <v>2972</v>
+        <v>3812</v>
       </c>
       <c r="E3" t="n">
-        <v>296</v>
+        <v>497</v>
       </c>
       <c r="F3" t="n">
         <v>23</v>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>454321</v>
+        <v>132312</v>
       </c>
       <c r="D4" t="n">
-        <v>7260</v>
+        <v>2972</v>
       </c>
       <c r="E4" t="n">
-        <v>956</v>
+        <v>296</v>
       </c>
       <c r="F4" t="n">
-        <v>559</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -554,17 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48672</v>
+        <v>77190</v>
       </c>
       <c r="D6" t="n">
-        <v>1768</v>
+        <v>2236</v>
       </c>
       <c r="E6" t="n">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="F6" t="n">
         <v>23</v>
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16236</v>
+        <v>56132</v>
       </c>
       <c r="D8" t="n">
-        <v>1020</v>
+        <v>1984</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15180</v>
+        <v>22663</v>
       </c>
       <c r="D9" t="n">
-        <v>988</v>
+        <v>1216</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77190</v>
+        <v>90423</v>
       </c>
       <c r="D10" t="n">
-        <v>2236</v>
+        <v>2624</v>
       </c>
       <c r="E10" t="n">
-        <v>249</v>
+        <v>481</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54522</v>
+        <v>15180</v>
       </c>
       <c r="D11" t="n">
-        <v>1868</v>
+        <v>988</v>
       </c>
       <c r="E11" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22663</v>
+        <v>48672</v>
       </c>
       <c r="D12" t="n">
-        <v>1216</v>
+        <v>1768</v>
       </c>
       <c r="E12" t="n">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="F12" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16236</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>54522</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1868</v>
+      </c>
+      <c r="E14" t="n">
+        <v>257</v>
+      </c>
+      <c r="F14" t="n">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13145.xlsx
+++ b/output/roomself_excel/13145.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3748</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>483</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>23</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>3812</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>497</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +555,20 @@
       <c r="D4" t="n">
         <v>2972</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>296</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>23</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +585,27 @@
       <c r="D5" t="n">
         <v>3212</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>358</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>445</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +623,26 @@
       <c r="D6" t="n">
         <v>2236</v>
       </c>
-      <c r="E6" t="n">
-        <v>249</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
+        <v>310</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>238</v>
+      </c>
+      <c r="J6" t="n">
         <v>23</v>
       </c>
     </row>
@@ -585,12 +661,12 @@
       <c r="D7" t="n">
         <v>1524</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +683,12 @@
       <c r="D8" t="n">
         <v>1984</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +705,20 @@
       <c r="D9" t="n">
         <v>1216</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>173</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>23</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +735,27 @@
       <c r="D10" t="n">
         <v>2624</v>
       </c>
-      <c r="E10" t="n">
-        <v>481</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>208</v>
+        <v>394</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>459</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +773,20 @@
       <c r="D11" t="n">
         <v>988</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +803,20 @@
       <c r="D12" t="n">
         <v>1768</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>208</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>23</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +833,12 @@
       <c r="D13" t="n">
         <v>1020</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +855,27 @@
       <c r="D14" t="n">
         <v>1868</v>
       </c>
-      <c r="E14" t="n">
-        <v>257</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>256</v>
+        <v>233</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>234</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
